--- a/testdata/DynaminData.xlsx
+++ b/testdata/DynaminData.xlsx
@@ -12,39 +12,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
   <si>
-    <t>name</t>
+    <t>2</t>
   </si>
   <si>
-    <t>spouse's</t>
-  </si>
-  <si>
-    <t>DOM</t>
-  </si>
-  <si>
-    <t>chirag</t>
-  </si>
-  <si>
-    <t>neha</t>
-  </si>
-  <si>
-    <t>6th</t>
-  </si>
-  <si>
-    <t>june</t>
-  </si>
-  <si>
-    <t>arun</t>
-  </si>
-  <si>
-    <t>archana</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>may</t>
+    <t>3</t>
   </si>
 </sst>
 </file>
@@ -89,49 +62,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="0">
         <v>0</v>
       </c>
-      <c r="B1" t="s" s="0">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s" s="0">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s" s="0">
-        <v>2</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s" s="0">
-        <v>3</v>
-      </c>
-      <c r="B2" t="s" s="0">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s" s="0">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s" s="0">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="0">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s" s="0">
-        <v>8</v>
-      </c>
-      <c r="C3" t="s" s="0">
-        <v>9</v>
-      </c>
-      <c r="D3" t="s" s="0">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
